--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -499,7 +499,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>更新日期：2024.10.10 07:31:09</t>
+          <t>更新日期：2024.10.10 13:18:14</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
@@ -3670,12 +3670,12 @@
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>maa://23020, maa://29023, maa://34319, *maa://39515</t>
+          <t>maa://23020, maa://29023, maa://34319, *maa://39515, maa://41690</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -499,7 +499,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>更新日期：2024.10.17 12:52:30</t>
+          <t>更新日期：2024.10.17 13:18:35</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -499,7 +499,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>更新日期：2024.10.20 13:17:20</t>
+          <t>更新日期：2024.10.21 13:19:04</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -499,7 +499,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>更新日期：2024.10.23 13:18:28</t>
+          <t>更新日期：2024.10.24 13:19:30</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="D324" s="10" t="inlineStr">
         <is>
-          <t>**maa://42224, maa://42299</t>
+          <t>maa://42299, **maa://42224</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="D330" s="10" t="inlineStr">
         <is>
-          <t>*maa://40957, *maa://41128, *maa://41035</t>
+          <t>maa://40957, *maa://41128, maa://41035</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -505,7 +505,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2024.12.08 15:46:46</t>
+          <t>更新日期：2024.12.10 13:19:52</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
@@ -976,12 +976,12 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://44401</t>
         </is>
       </c>
       <c r="F15" s="8" t="n"/>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>*maa://42970</t>
+          <t>maa://42970</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -505,7 +505,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.02.22 13:17:25</t>
+          <t>更新日期：2025.02.26 13:18:30</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>maa://20966</t>
+          <t>*maa://20966</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>maa://25018, maa://25776, maa://28361, maa://25772, *maa://25161, maa://32653, *maa://45194</t>
+          <t>maa://25018, maa://25776, maa://28361, maa://25772, *maa://25161, maa://32653, maa://45194</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -505,7 +505,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.02 13:19:18</t>
+          <t>更新日期：2025.03.03 13:19:02</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -505,7 +505,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.02 13:19:18</t>
+          <t>更新日期：2025.03.05 13:18:50</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>maa://20975, maa://30806</t>
+          <t>maa://20975, maa://30806, **maa://47950</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB368"/>
+  <dimension ref="A1:AB369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.5" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -505,7 +505,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.08 16:37:02</t>
+          <t>更新日期：2025.03.09 13:14:58</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
@@ -6597,17 +6597,17 @@
       </c>
       <c r="B262" s="15" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D262" s="10" t="inlineStr">
         <is>
-          <t>*maa://20825, *maa://21445, *maa://35726</t>
+          <t>maa://48265</t>
         </is>
       </c>
     </row>
@@ -6619,17 +6619,17 @@
       </c>
       <c r="B263" s="15" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D263" s="10" t="inlineStr">
         <is>
-          <t>maa://48265</t>
+          <t>*maa://20825, *maa://21445, *maa://35726</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="D276" s="10" t="inlineStr">
         <is>
-          <t>maa://48266, maa://48267</t>
+          <t>maa://48267, maa://48266</t>
         </is>
       </c>
     </row>
@@ -8940,6 +8940,28 @@
       <c r="D368" t="inlineStr">
         <is>
           <t>maa://47023</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="12" t="inlineStr">
+        <is>
+          <t>钼铅</t>
+        </is>
+      </c>
+      <c r="B369" s="12" t="inlineStr">
+        <is>
+          <t>9-6</t>
+        </is>
+      </c>
+      <c r="C369" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB368"/>
+  <dimension ref="A1:AB369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.5" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -505,7 +505,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.08 16:37:02</t>
+          <t>更新日期：2025.03.10 13:15:47</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
@@ -6597,17 +6597,17 @@
       </c>
       <c r="B262" s="15" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D262" s="10" t="inlineStr">
         <is>
-          <t>*maa://20825, *maa://21445, *maa://35726</t>
+          <t>maa://48265</t>
         </is>
       </c>
     </row>
@@ -6619,17 +6619,17 @@
       </c>
       <c r="B263" s="15" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D263" s="10" t="inlineStr">
         <is>
-          <t>maa://48265</t>
+          <t>*maa://20825, *maa://21445, *maa://35726</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="D276" s="10" t="inlineStr">
         <is>
-          <t>maa://48266, maa://48267</t>
+          <t>maa://48267, maa://48266</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="C331" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D331" s="13" t="inlineStr">
         <is>
-          <t>maa://32647, maa://32415, maa://34677, maa://32892</t>
+          <t>maa://32647, maa://32415, maa://34677, maa://32892, maa://47851</t>
         </is>
       </c>
     </row>
@@ -8940,6 +8940,28 @@
       <c r="D368" t="inlineStr">
         <is>
           <t>maa://47023</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="12" t="inlineStr">
+        <is>
+          <t>钼铅</t>
+        </is>
+      </c>
+      <c r="B369" s="12" t="inlineStr">
+        <is>
+          <t>9-6</t>
+        </is>
+      </c>
+      <c r="C369" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -505,7 +505,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.20 13:18:45</t>
+          <t>更新日期：2025.03.21 13:18:27</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -505,7 +505,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.28 13:20:26</t>
+          <t>更新日期：2025.03.29 13:18:03</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C236" s="12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D236" s="10" t="inlineStr">
         <is>
-          <t>*maa://30667, maa://30666, *maa://26836, maa://37607, *maa://34428, *maa://30723, maa://39588, *maa://37850</t>
+          <t>*maa://30667, maa://30666, *maa://26836, maa://37607, *maa://34428, *maa://30723, maa://39588, *maa://37850, maa://49172</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -505,7 +505,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.04.17 13:19:49</t>
+          <t>更新日期：2025.04.19 13:19:27</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>maa://29633, maa://29627, maa://29659, **maa://30679, maa://29861, maa://42343, maa://49074</t>
+          <t>maa://29633, maa://29627, maa://29659, **maa://30679, maa://29861, maa://49074, maa://42343</t>
         </is>
       </c>
     </row>
@@ -8736,12 +8736,12 @@
       </c>
       <c r="C359" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>maa://42333, maa://41977</t>
+          <t>maa://42333, maa://41977, maa://50518</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -505,7 +505,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.05.24 13:19:10</t>
+          <t>更新日期：2025.05.31 13:19:45</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>maa://20990</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -596,12 +596,12 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>*maa://20996</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
@@ -632,12 +632,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>maa://41855</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F5" s="6" t="n"/>
@@ -668,12 +668,12 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>*maa://20925</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F6" s="6" t="n"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>maa://20850</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F7" s="8" t="n"/>
@@ -738,12 +738,12 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>maa://20980</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
@@ -772,12 +772,12 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>maa://20941</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F9" s="8" t="n"/>
@@ -806,12 +806,12 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>*maa://20888</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F10" s="8" t="n"/>
@@ -840,12 +840,12 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>maa://20866</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F11" s="8" t="n"/>
@@ -874,12 +874,12 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>maa://20857</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F12" s="8" t="n"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>maa://37695</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F13" s="8" t="n"/>
@@ -942,12 +942,12 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>maa://39023</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F14" s="8" t="n"/>
@@ -976,12 +976,12 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>maa://44401</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F15" s="8" t="n"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>maa://20919, *maa://31611</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F16" s="8" t="n"/>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>*maa://20848</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F17" s="8" t="n"/>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>maa://20930</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F18" s="8" t="n"/>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>maa://20897</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F19" s="8" t="n"/>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>maa://20865, maa://20826</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F20" s="8" t="n"/>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>maa://20900</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F21" s="8" t="n"/>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>maa://20948, maa://30844</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F22" s="8" t="n"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>maa://20876</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F23" s="8" t="n"/>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>maa://45260</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F24" s="8" t="n"/>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>maa://20864</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F25" s="8" t="n"/>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>maa://44220</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F26" s="8" t="n"/>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>*maa://20849, *maa://28758, maa://29036, *maa://42172, maa://30285</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F27" s="8" t="n"/>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>maa://20920</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F28" s="8" t="n"/>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>maa://20863, maa://20832, maa://20727</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F29" s="8" t="n"/>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>*maa://20871</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F30" s="8" t="n"/>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>**maa://39024</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>maa://36644, maa://36866, maa://45572, maa://27794, maa://20843, maa://20960, **maa://24483, maa://20862, *maa://20893</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>maa://30500, *maa://27290</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>maa://20916, *maa://52658</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>maa://20847</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>maa://20997</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>maa://27376, maa://42635, **maa://20838</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>maa://20962</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>*maa://29012, maa://20928</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>maa://20882</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>maa://20892</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>maa://20918, maa://34883, maa://20824</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>maa://20889</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>maa://34718</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>maa://20910</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>maa://39025</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>maa://20938</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1894,12 +1894,12 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>maa://20954</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>*maa://32845, *maa://20982</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>maa://30503</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>maa://21001</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>maa://42295</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>maa://20953, maa://31173</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>maa://30502</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>maa://20932, maa://42415, maa://40838</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>maa://44235, maa://45604, maa://20961, maa://44220, maa://20910</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>*maa://20965</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>maa://28900, maa://30126</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>maa://27970, maa://41118</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2158,12 +2158,12 @@
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>maa://38298</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>maa://20841, maa://24093, maa://31559, maa://20924, maa://25777, maa://20631, maa://28241</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>maa://20844</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>*maa://20845, maa://38727</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>maa://28187, maa://33504, maa://45144, maa://43531</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>maa://28567, maa://30525, maa://38735, *maa://28188, maa://30524</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>maa://20993, maa://20914, maa://45606, maa://20829, maa://40159, maa://20900</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>maa://39693, maa://49348</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>maa://20976, maa://20815</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2356,12 +2356,12 @@
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>maa://20974, maa://29079, maa://29096, maa://29087, *maa://20823, maa://20855, maa://20904</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>maa://20944, maa://35393</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2400,12 @@
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>maa://20943, maa://30673, maa://30672, maa://20856</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2422,12 +2422,12 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>maa://36643, maa://36864, maa://39140</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>maa://39139</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>maa://39142</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2488,12 +2488,12 @@
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>maa://20989</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>maa://20873</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>maa://20958</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>maa://20957</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>maa://20875</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>maa://20952</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2620,12 +2620,12 @@
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>maa://30525, maa://20859, *maa://28188, maa://30524</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>maa://28072</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>maa://45572, maa://27794, maa://20960</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>maa://20972</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2708,12 +2708,12 @@
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>maa://20874</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2730,12 +2730,12 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>maa://20885</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2752,12 @@
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>maa://20886</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>maa://24472, *maa://35841</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2796,12 +2796,12 @@
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>maa://44402</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>*maa://28190, maa://20880</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2840,12 +2840,12 @@
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>maa://24609</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>maa://20890</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2884,12 @@
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>maa://20984</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>maa://40157</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2928,12 +2928,12 @@
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>maa://20927</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>*maa://20926</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>maa://20991, maa://51015</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>maa://20967</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3016,12 @@
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>maa://20929</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>maa://20852</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>maa://45572, maa://27794, *maa://20893</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3082,12 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>maa://40517, *maa://39240</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>*maa://29094, maa://28904</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>*maa://20966</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>maa://39143</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>maa://45572, maa://27794, maa://20843, **maa://24483</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>maa://20894</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3214,12 +3214,12 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>maa://25018, maa://51881, maa://25776, maa://28361, maa://25772, maa://32653, maa://25161, maa://45194, maa://56588</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>maa://45259</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>maa://20887</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>*maa://28554</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>maa://20933, maa://20822</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>maa://29037</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>maa://20904</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>maa://20908, maa://35723, *maa://23346, maa://38822</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3390,12 +3390,12 @@
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>maa://29659, maa://29031</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3412,12 +3412,12 @@
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>maa://31560, maa://20940</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>maa://20986</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>maa://31560, maa://20851</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>maa://20949</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3500,12 @@
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>maa://20869, maa://44690</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>maa://29650, maa://45570</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>maa://20868</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>*maa://20909</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>maa://44403</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>maa://30501</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3632,12 +3632,12 @@
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>maa://20914, maa://31937, maa://20829</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>maa://37484, maa://24611</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>maa://24491, maa://24493</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>maa://21422</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3720,12 +3720,12 @@
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>maa://30719</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>maa://20837, maa://37666</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>maa://29023, maa://39515</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3786,12 +3786,12 @@
       </c>
       <c r="C134" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>maa://39146</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>maa://20856</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>maa://20913</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3852,12 +3852,12 @@
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>maa://41856</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3874,12 @@
       </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>maa://29025</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>**maa://30679, maa://45258</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>maa://20981</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>maa://37689</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3962,12 +3962,12 @@
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>maa://28484, maa://31185, maa://30306</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3984,12 +3984,12 @@
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>maa://30670, maa://31470, *maa://45066</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4006,12 +4006,12 @@
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>maa://20971</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4028,12 +4028,12 @@
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>maa://39147</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>maa://20898</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4072,12 +4072,12 @@
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>maa://29056</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>maa://28828, maa://20846, **maa://47286</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>maa://36641, maa://40957, maa://36865, maa://44635, maa://44660, maa://41128, maa://42918, maa://44119, maa://46108, maa://37300, maa://42917</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>maa://51549, maa://51923</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4160,12 +4160,12 @@
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>maa://20961</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4182,12 +4182,12 @@
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>maa://20963</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>maa://39148</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>maa://20946, maa://20833</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>maa://20945</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="C156" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>maa://37694</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>**maa://39149</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="C158" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>maa://20959</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>maa://44232, maa://45603, maa://44305</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C160" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>maa://20936</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>maa://20855</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4402,12 @@
       </c>
       <c r="C162" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>maa://40158</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>*maa://32845, maa://29054</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4446,12 +4446,12 @@
       </c>
       <c r="C164" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>maa://20973</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>maa://39150</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="C166" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>maa://20975, maa://30806, *maa://47950</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>maa://29633, maa://29627, maa://29659, maa://49074, **maa://30679, maa://29861, maa://42343</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="C168" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>maa://49655, maa://49867</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>maa://29059</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4578,12 +4578,12 @@
       </c>
       <c r="C170" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>maa://45556</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>maa://40159</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4622,12 +4622,12 @@
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>maa://39152</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4644,12 +4644,12 @@
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>*maa://20905</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4666,12 +4666,12 @@
       </c>
       <c r="C174" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>maa://32418, maa://51440</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4688,12 +4688,12 @@
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>maa://37690</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4710,12 +4710,12 @@
       </c>
       <c r="C176" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>maa://20842</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4732,12 +4732,12 @@
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>maa://20912</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>maa://20911, *maa://29012</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4776,12 +4776,12 @@
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>maa://20964</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="C180" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>maa://20983</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4820,12 +4820,12 @@
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>maa://31560, *maa://20968</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="C182" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>maa://28104</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4864,12 +4864,12 @@
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>maa://20861</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4886,12 +4886,12 @@
       </c>
       <c r="C184" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>maa://20970</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4908,12 +4908,12 @@
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>maa://20969, maa://41303</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4930,12 +4930,12 @@
       </c>
       <c r="C186" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>maa://20999</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4952,12 +4952,12 @@
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>maa://35198</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4974,12 +4974,12 @@
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>maa://39153</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>maa://34866, maa://34714</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5018,12 @@
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>maa://34883, maa://20895</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>maa://20853</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>maa://20942</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>maa://20992</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>*maa://28190, maa://20994</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5128,12 +5128,12 @@
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>maa://20860</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>maa://44224, maa://35854, maa://25760, maa://50388, **maa://20872, maa://51066</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>maa://39156, *maa://39550, *maa://53417</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>maa://27823, *maa://28190, maa://22894, *maa://20906</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5216,12 +5216,12 @@
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>maa://27823, *maa://28190, maa://22894, *maa://20906</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5238,12 +5238,12 @@
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>maa://42223, maa://49077, maa://42292, maa://42402</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>maa://39154</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="C202" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>maa://20854</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>maa://20937</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5326,12 +5326,12 @@
       </c>
       <c r="C204" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>maa://22468</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5348,12 +5348,12 @@
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>maa://30673, maa://30672</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>maa://20934, maa://20827, maa://20828</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>maa://20935</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="C208" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D208" s="10" t="inlineStr">
         <is>
-          <t>maa://53354</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5436,12 +5436,12 @@
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>maa://28133, maa://25369</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5458,12 +5458,12 @@
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>maa://20956, *maa://20830, maa://44703</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5480,12 +5480,12 @@
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>*maa://20955</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5502,12 +5502,12 @@
       </c>
       <c r="C212" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
         <is>
-          <t>maa://39238</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>maa://45261</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5546,12 +5546,12 @@
       </c>
       <c r="C214" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D214" s="10" t="inlineStr">
         <is>
-          <t>maa://39694</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5568,12 +5568,12 @@
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>maa://24636, maa://25778</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5590,12 +5590,12 @@
       </c>
       <c r="C216" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D216" s="10" t="inlineStr">
         <is>
-          <t>maa://48261</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D217" s="10" t="inlineStr">
         <is>
-          <t>*maa://39157</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D219" s="10" t="inlineStr">
         <is>
-          <t>maa://26499</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5678,12 +5678,12 @@
       </c>
       <c r="C220" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>maa://20858</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5700,12 +5700,12 @@
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
         <is>
-          <t>maa://39695</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5722,12 +5722,12 @@
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>maa://20988</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
-          <t>maa://39158</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5766,12 +5766,12 @@
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D224" s="10" t="inlineStr">
         <is>
-          <t>maa://28187, maa://43531, maa://39520</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5788,12 +5788,12 @@
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D225" s="10" t="inlineStr">
         <is>
-          <t>maa://20985</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5810,12 +5810,12 @@
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D226" s="10" t="inlineStr">
         <is>
-          <t>maa://20987, *maa://35801</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5832,12 +5832,12 @@
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D227" s="10" t="inlineStr">
         <is>
-          <t>*maa://29644, maa://39159</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="C228" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D228" s="10" t="inlineStr">
         <is>
-          <t>maa://30677</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D229" s="10" t="inlineStr">
         <is>
-          <t>maa://20896</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5898,12 +5898,12 @@
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D230" s="10" t="inlineStr">
         <is>
-          <t>maa://29058, maa://39140, maa://38723</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5920,12 +5920,12 @@
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>*maa://48263</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5942,12 +5942,12 @@
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D232" s="10" t="inlineStr">
         <is>
-          <t>maa://39160</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D233" s="10" t="inlineStr">
         <is>
-          <t>maa://49491</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5986,12 +5986,12 @@
       </c>
       <c r="C234" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D234" s="10" t="inlineStr">
         <is>
-          <t>maa://35952</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6008,12 +6008,12 @@
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D235" s="10" t="inlineStr">
         <is>
-          <t>maa://20917</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C236" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D236" s="10" t="inlineStr">
         <is>
-          <t>maa://30714, maa://30675</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6052,12 +6052,12 @@
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D237" s="13" t="inlineStr">
         <is>
-          <t>maa://20922, *maa://32623, maa://34242</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="C238" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D238" s="10" t="inlineStr">
         <is>
-          <t>maa://32999</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D239" s="10" t="inlineStr">
         <is>
-          <t>*maa://30667, maa://30666, *maa://30723, maa://39588</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6118,12 +6118,12 @@
       </c>
       <c r="C240" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D240" s="10" t="inlineStr">
         <is>
-          <t>maa://30512</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6140,12 +6140,12 @@
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D241" s="10" t="inlineStr">
         <is>
-          <t>maa://20870</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6162,12 +6162,12 @@
       </c>
       <c r="C242" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D242" s="10" t="inlineStr">
         <is>
-          <t>maa://29024</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6184,12 +6184,12 @@
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D243" s="10" t="inlineStr">
         <is>
-          <t>maa://20867, maa://38485, *maa://32202</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6206,12 +6206,12 @@
       </c>
       <c r="C244" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>maa://40160</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D245" s="10" t="inlineStr">
         <is>
-          <t>maa://43089</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6250,12 +6250,12 @@
       </c>
       <c r="C246" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D246" s="10" t="inlineStr">
         <is>
-          <t>maa://30674</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6272,12 +6272,12 @@
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D247" s="10" t="inlineStr">
         <is>
-          <t>maa://28923, maa://28906</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="C248" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D248" s="10" t="inlineStr">
         <is>
-          <t>maa://42287, maa://45570, maa://42225</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D249" s="13" t="inlineStr">
         <is>
-          <t>maa://39161</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D250" s="10" t="inlineStr">
         <is>
-          <t>maa://20923</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D251" s="10" t="inlineStr">
         <is>
-          <t>maa://24093, maa://31559, maa://20924, *maa://49440</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="C252" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D252" s="10" t="inlineStr">
         <is>
-          <t>maa://40958, *maa://45067</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D253" s="10" t="inlineStr">
         <is>
-          <t>maa://20840</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="C254" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D254" s="10" t="inlineStr">
         <is>
-          <t>maa://20877, *maa://45067, maa://20836, maa://20632</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D255" s="10" t="inlineStr">
         <is>
-          <t>maa://20879, maa://20834</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6470,12 +6470,12 @@
       </c>
       <c r="C256" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D256" s="10" t="inlineStr">
         <is>
-          <t>maa://20839</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6492,12 +6492,12 @@
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D257" s="10" t="inlineStr">
         <is>
-          <t>maa://30676</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6514,12 +6514,12 @@
       </c>
       <c r="C258" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D258" s="10" t="inlineStr">
         <is>
-          <t>maa://31560, maa://20884</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D259" s="10" t="inlineStr">
         <is>
-          <t>maa://47204</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6558,12 +6558,12 @@
       </c>
       <c r="C260" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D260" s="10" t="inlineStr">
         <is>
-          <t>maa://29027</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6580,12 +6580,12 @@
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D261" s="10" t="inlineStr">
         <is>
-          <t>maa://20977</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6602,12 +6602,12 @@
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D262" s="10" t="inlineStr">
         <is>
-          <t>maa://39162</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D263" s="10" t="inlineStr">
         <is>
-          <t>maa://22467</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D265" s="10" t="inlineStr">
         <is>
-          <t>maa://49643</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="C266" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D266" s="10" t="inlineStr">
         <is>
-          <t>maa://48265</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6712,12 +6712,12 @@
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D267" s="10" t="inlineStr">
         <is>
-          <t>*maa://20825, *maa://21445, *maa://35726</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6734,12 @@
       </c>
       <c r="C268" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D268" s="10" t="inlineStr">
         <is>
-          <t>maa://25769</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6756,12 +6756,12 @@
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D269" s="10" t="inlineStr">
         <is>
-          <t>maa://20862</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6778,12 +6778,12 @@
       </c>
       <c r="C270" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D270" s="10" t="inlineStr">
         <is>
-          <t>maa://51881, maa://51630, maa://51893, *maa://55171, maa://56588</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D271" s="10" t="inlineStr">
         <is>
-          <t>maa://39163</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6822,12 +6822,12 @@
       </c>
       <c r="C272" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D272" s="10" t="inlineStr">
         <is>
-          <t>maa://29061</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D273" s="10" t="inlineStr">
         <is>
-          <t>maa://20939</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6866,12 +6866,12 @@
       </c>
       <c r="C274" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D274" s="10" t="inlineStr">
         <is>
-          <t>maa://39164</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6888,12 +6888,12 @@
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D275" s="10" t="inlineStr">
         <is>
-          <t>maa://28133, maa://33394</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6910,12 +6910,12 @@
       </c>
       <c r="C276" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D276" s="10" t="inlineStr">
         <is>
-          <t>maa://42311</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6932,12 +6932,12 @@
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D277" s="10" t="inlineStr">
         <is>
-          <t>maa://41362</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6954,12 +6954,12 @@
       </c>
       <c r="C278" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D278" s="10" t="inlineStr">
         <is>
-          <t>maa://20978</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6976,12 +6976,12 @@
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D279" s="10" t="inlineStr">
         <is>
-          <t>maa://21002</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="C280" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D280" s="10" t="inlineStr">
         <is>
-          <t>*maa://39165</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7020,12 +7020,12 @@
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D281" s="10" t="inlineStr">
         <is>
-          <t>maa://48267, maa://48266</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7042,12 +7042,12 @@
       </c>
       <c r="C282" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D282" s="10" t="inlineStr">
         <is>
-          <t>maa://29635</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D283" s="10" t="inlineStr">
         <is>
-          <t>maa://38296</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7086,12 +7086,12 @@
       </c>
       <c r="C284" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D284" s="10" t="inlineStr">
         <is>
-          <t>maa://20899, maa://46332</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D285" s="10" t="inlineStr">
         <is>
-          <t>maa://53353</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7130,12 +7130,12 @@
       </c>
       <c r="C286" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D286" s="10" t="inlineStr">
         <is>
-          <t>maa://20881</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7152,12 +7152,12 @@
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D287" s="10" t="inlineStr">
         <is>
-          <t>maa://30710, maa://36845, maa://31558, maa://30668</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7174,12 +7174,12 @@
       </c>
       <c r="C288" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D288" s="10" t="inlineStr">
         <is>
-          <t>maa://20902</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7196,12 +7196,12 @@
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D289" s="10" t="inlineStr">
         <is>
-          <t>maa://29159</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="C290" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D290" s="10" t="inlineStr">
         <is>
-          <t>maa://25774, maa://28133, maa://22469, **maa://31349</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7240,12 +7240,12 @@
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D291" s="10" t="inlineStr">
         <is>
-          <t>maa://47882</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="C292" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D292" s="10" t="inlineStr">
         <is>
-          <t>maa://32414, maa://32505, maa://39155</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7284,12 +7284,12 @@
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D293" s="10" t="inlineStr">
         <is>
-          <t>maa://45799, maa://57199</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7306,12 +7306,12 @@
       </c>
       <c r="C294" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D294" s="10" t="inlineStr">
         <is>
-          <t>maa://42312</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D295" s="10" t="inlineStr">
         <is>
-          <t>maa://36642, maa://36867, maa://39155</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="C296" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D296" s="10" t="inlineStr">
         <is>
-          <t>**maa://39166, maa://39167</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7372,12 +7372,12 @@
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D297" s="10" t="inlineStr">
         <is>
-          <t>maa://29005, maa://31560</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="C298" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D298" s="10" t="inlineStr">
         <is>
-          <t>maa://39168</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D299" s="10" t="inlineStr">
         <is>
-          <t>maa://39169</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7438,12 +7438,12 @@
       </c>
       <c r="C300" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D300" s="10" t="inlineStr">
         <is>
-          <t>maa://39170</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7460,12 +7460,12 @@
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D301" s="10" t="inlineStr">
         <is>
-          <t>maa://50280, maa://49642, maa://49660, *maa://50517</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7482,12 +7482,12 @@
       </c>
       <c r="C302" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D302" s="10" t="inlineStr">
         <is>
-          <t>maa://39171</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7504,12 +7504,12 @@
       </c>
       <c r="C303" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D303" s="10" t="inlineStr">
         <is>
-          <t>maa://27939</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7526,12 +7526,12 @@
       </c>
       <c r="C304" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D304" s="10" t="inlineStr">
         <is>
-          <t>maa://53352</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7548,12 +7548,12 @@
       </c>
       <c r="C305" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D305" s="10" t="inlineStr">
         <is>
-          <t>maa://29129</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7570,12 +7570,12 @@
       </c>
       <c r="C306" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D306" s="10" t="inlineStr">
         <is>
-          <t>maa://36005</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7592,12 +7592,12 @@
       </c>
       <c r="C307" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D307" s="10" t="inlineStr">
         <is>
-          <t>maa://35859</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7614,12 +7614,12 @@
       </c>
       <c r="C308" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D308" s="10" t="inlineStr">
         <is>
-          <t>maa://53348</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7636,12 +7636,12 @@
       </c>
       <c r="C309" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D309" s="10" t="inlineStr">
         <is>
-          <t>**maa://39172</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="C310" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D310" s="10" t="inlineStr">
         <is>
-          <t>maa://39173</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="C311" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D311" s="10" t="inlineStr">
         <is>
-          <t>maa://25775, *maa://25393</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7702,12 +7702,12 @@
       </c>
       <c r="C312" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D312" s="10" t="inlineStr">
         <is>
-          <t>maa://40161</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="C313" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D313" s="10" t="inlineStr">
         <is>
-          <t>maa://25367</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7746,12 +7746,12 @@
       </c>
       <c r="C314" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D314" s="10" t="inlineStr">
         <is>
-          <t>*maa://43090</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7768,12 +7768,12 @@
       </c>
       <c r="C315" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D315" s="10" t="inlineStr">
         <is>
-          <t>maa://28070</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7790,12 +7790,12 @@
       </c>
       <c r="C316" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D316" s="10" t="inlineStr">
         <is>
-          <t>maa://28241</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7812,12 +7812,12 @@
       </c>
       <c r="C317" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D317" s="10" t="inlineStr">
         <is>
-          <t>maa://25773, *maa://26088</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="C318" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D318" s="10" t="inlineStr">
         <is>
-          <t>maa://39239</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7856,12 +7856,12 @@
       </c>
       <c r="C319" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D319" s="10" t="inlineStr">
         <is>
-          <t>maa://39692, maa://39810</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7878,12 +7878,12 @@
       </c>
       <c r="C320" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D320" s="10" t="inlineStr">
         <is>
-          <t>*maa://39174</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="C321" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D321" s="10" t="inlineStr">
         <is>
-          <t>maa://39175</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="C322" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D322" s="10" t="inlineStr">
         <is>
-          <t>maa://34867, maa://34715</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7944,12 +7944,12 @@
       </c>
       <c r="C323" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D323" s="10" t="inlineStr">
         <is>
-          <t>maa://39176</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7966,12 +7966,12 @@
       </c>
       <c r="C324" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D324" s="10" t="inlineStr">
         <is>
-          <t>maa://42316</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7988,12 +7988,12 @@
       </c>
       <c r="C325" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D325" s="10" t="inlineStr">
         <is>
-          <t>maa://30680</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="C326" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D326" s="10" t="inlineStr">
         <is>
-          <t>maa://40956</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="C328" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D328" s="10" t="inlineStr">
         <is>
-          <t>maa://34205, **maa://39541</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8076,12 +8076,12 @@
       </c>
       <c r="C329" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D329" s="10" t="inlineStr">
         <is>
-          <t>maa://43092, maa://43093</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8098,12 @@
       </c>
       <c r="C330" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D330" s="10" t="inlineStr">
         <is>
-          <t>maa://44234</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="C331" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D331" s="13" t="inlineStr">
         <is>
-          <t>maa://42968, maa://49245</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8142,12 +8142,12 @@
       </c>
       <c r="C332" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D332" s="13" t="inlineStr">
         <is>
-          <t>*maa://40162</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8164,12 +8164,12 @@
       </c>
       <c r="C333" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D333" s="13" t="inlineStr">
         <is>
-          <t>maa://37692</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8186,12 +8186,12 @@
       </c>
       <c r="C334" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D334" s="13" t="inlineStr">
         <is>
-          <t>maa://30671, maa://30669, maa://37275, *maa://32410, maa://41605</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8208,12 +8208,12 @@
       </c>
       <c r="C335" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D335" s="13" t="inlineStr">
         <is>
-          <t>maa://38295, maa://49332</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8230,12 +8230,12 @@
       </c>
       <c r="C336" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D336" s="13" t="inlineStr">
         <is>
-          <t>maa://32417</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8252,12 +8252,12 @@
       </c>
       <c r="C337" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D337" s="13" t="inlineStr">
         <is>
-          <t>maa://32419</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8274,12 +8274,12 @@
       </c>
       <c r="C338" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>maa://32416</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8296,12 +8296,12 @@
       </c>
       <c r="C339" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>maa://45800</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C340" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>maa://32647, maa://32415, maa://34677, maa://32892, maa://32653</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8340,12 +8340,12 @@
       </c>
       <c r="C341" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>maa://32420</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8362,12 +8362,12 @@
       </c>
       <c r="C342" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>maa://35606</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8384,12 +8384,12 @@
       </c>
       <c r="C343" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>maa://34716</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="C344" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>maa://39179</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="C345" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>maa://34865, maa://34717, *maa://45066</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8450,12 +8450,12 @@
       </c>
       <c r="C346" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>maa://39180</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8472,12 +8472,12 @@
       </c>
       <c r="C347" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>maa://45834, maa://45833</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8494,12 +8494,12 @@
       </c>
       <c r="C348" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>maa://39181</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8516,12 +8516,12 @@
       </c>
       <c r="C349" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>maa://36868, maa://35996, maa://47349</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8538,12 +8538,12 @@
       </c>
       <c r="C350" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>maa://36647</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8560,12 +8560,12 @@
       </c>
       <c r="C351" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>maa://42299, maa://42224</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="C352" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>maa://49648, *maa://49662</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8604,12 +8604,12 @@
       </c>
       <c r="C353" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>maa://36646, maa://36845, maa://51007</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8626,12 +8626,12 @@
       </c>
       <c r="C354" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>maa://36645, maa://36841, maa://37484, maa://37858, maa://40489, maa://56268</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8648,12 +8648,12 @@
       </c>
       <c r="C355" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>maa://42635, maa://50629, maa://48859</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8670,12 +8670,12 @@
       </c>
       <c r="C356" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>maa://39183</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8692,12 @@
       </c>
       <c r="C357" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>maa://39184</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="C358" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>maa://40957, maa://44635, maa://48026, maa://41035, maa://44660, maa://41128</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8736,12 +8736,12 @@
       </c>
       <c r="C359" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>maa://40164</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8758,12 +8758,12 @@
       </c>
       <c r="C360" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>maa://48268</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="C361" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>maa://40165</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="C362" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>maa://45798</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8824,12 +8824,12 @@
       </c>
       <c r="C363" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>maa://42331</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8846,12 +8846,12 @@
       </c>
       <c r="C364" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>maa://42333, maa://41977, maa://50518</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8868,12 +8868,12 @@
       </c>
       <c r="C365" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>maa://42338, maa://41976</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8890,12 +8890,12 @@
       </c>
       <c r="C366" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>maa://41110, maa://45605</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8912,12 +8912,12 @@
       </c>
       <c r="C367" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>maa://42343</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="C368" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>maa://43095</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8956,12 +8956,12 @@
       </c>
       <c r="C369" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>maa://44233, maa://45570</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="C370" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>maa://43097</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9000,12 +9000,12 @@
       </c>
       <c r="C371" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>maa://43872</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9022,12 +9022,12 @@
       </c>
       <c r="C372" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>maa://53307</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="C373" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>maa://43875</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="C374" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>maa://42970, maa://44745, **maa://49516, *maa://45952, maa://44896</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9088,12 +9088,12 @@
       </c>
       <c r="C375" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>maa://44389</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="C376" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>maa://48113</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9132,12 +9132,12 @@
       </c>
       <c r="C377" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>maa://45807</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9154,12 +9154,12 @@
       </c>
       <c r="C378" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>maa://50552</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9176,12 +9176,12 @@
       </c>
       <c r="C379" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>maa://47175, maa://47174</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9198,12 +9198,12 @@
       </c>
       <c r="C380" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>maa://47023</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9220,12 +9220,12 @@
       </c>
       <c r="C381" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>maa://48618</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="C382" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>maa://51907, maa://51908</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="C384" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>maa://51898, maa://57241</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9308,12 +9308,12 @@
       </c>
       <c r="C385" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>maa://51880, maa://51878, maa://56651</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9330,12 +9330,12 @@
       </c>
       <c r="C386" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>maa://51872, maa://51876, maa://51873</t>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单用户版.xlsx
+++ b/Excel/模组任务干员名单用户版.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB386"/>
+  <dimension ref="A1:AB392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.5" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -505,7 +505,7 @@
     <row r="1" ht="14.25" customHeight="1" s="3">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.05.24 13:19:10</t>
+          <t>更新日期：2025.06.07 13:19:20</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>maa://20990</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -596,12 +596,12 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>*maa://20996</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
@@ -632,12 +632,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>maa://41855</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F5" s="6" t="n"/>
@@ -668,12 +668,12 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>*maa://20925</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F6" s="6" t="n"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>maa://20850</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F7" s="8" t="n"/>
@@ -738,12 +738,12 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>maa://20980</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
@@ -772,12 +772,12 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>maa://20941</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F9" s="8" t="n"/>
@@ -806,12 +806,12 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>*maa://20888</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F10" s="8" t="n"/>
@@ -840,12 +840,12 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>maa://20866</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F11" s="8" t="n"/>
@@ -874,12 +874,12 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>maa://20857</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F12" s="8" t="n"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>maa://37695</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F13" s="8" t="n"/>
@@ -942,12 +942,12 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>maa://39023</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F14" s="8" t="n"/>
@@ -976,12 +976,12 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>maa://44401</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F15" s="8" t="n"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>maa://20919, *maa://31611</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F16" s="8" t="n"/>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>*maa://20848</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F17" s="8" t="n"/>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>maa://20930</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F18" s="8" t="n"/>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>maa://20897</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F19" s="8" t="n"/>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>maa://20865, maa://20826</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F20" s="8" t="n"/>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>maa://20900</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F21" s="8" t="n"/>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>maa://20948, maa://30844</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F22" s="8" t="n"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>maa://20876</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F23" s="8" t="n"/>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>maa://45260</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F24" s="8" t="n"/>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>maa://20864</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F25" s="8" t="n"/>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>maa://44220</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F26" s="8" t="n"/>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>*maa://20849, *maa://28758, maa://29036, *maa://42172, maa://30285</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F27" s="8" t="n"/>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>maa://20920</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F28" s="8" t="n"/>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>maa://20863, maa://20832, maa://20727</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F29" s="8" t="n"/>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>*maa://20871</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F30" s="8" t="n"/>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>**maa://39024</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>maa://36644, maa://36866, maa://45572, maa://27794, maa://20843, maa://20960, **maa://24483, maa://20862, *maa://20893</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>maa://30500, *maa://27290</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>maa://20916, *maa://52658</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>maa://20847</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>maa://20997</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>maa://27376, maa://42635, **maa://20838</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>maa://20962</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>*maa://29012, maa://20928</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>maa://20882</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>maa://20892</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>maa://20918, maa://34883, maa://20824</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>maa://20889</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>maa://34718</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>maa://20910</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>maa://39025</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>maa://20938</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1894,12 +1894,12 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>maa://20954</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>*maa://32845, *maa://20982</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>maa://30503</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>maa://21001</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>maa://42295</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>maa://20953, maa://31173</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>maa://30502</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>maa://20932, maa://42415, maa://40838</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>maa://44235, maa://45604, maa://20961, maa://44220, maa://20910</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>*maa://20965</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>maa://28900, maa://30126</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>maa://27970, maa://41118</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2158,12 +2158,12 @@
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>maa://38298</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>maa://20841, maa://24093, maa://31559, maa://20924, maa://25777, maa://20631, maa://28241</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>maa://20844</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>*maa://20845, maa://38727</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>maa://28187, maa://33504, maa://45144, maa://43531</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>maa://28567, maa://30525, maa://38735, *maa://28188, maa://30524</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>maa://20993, maa://20914, maa://45606, maa://20829, maa://40159, maa://20900</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>maa://39693, maa://49348</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>maa://20976, maa://20815</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2356,12 +2356,12 @@
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>maa://20974, maa://29079, maa://29096, maa://29087, *maa://20823, maa://20855, maa://20904</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>maa://20944, maa://35393</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2400,12 @@
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>maa://20943, maa://30673, maa://30672, maa://20856</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2422,12 +2422,12 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>maa://36643, maa://36864, maa://39140</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>maa://39139</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>maa://39142</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2488,12 +2488,12 @@
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>maa://20989</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>maa://20873</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>maa://20958</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>maa://20957</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>maa://20875</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>maa://20952</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2620,12 +2620,12 @@
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>maa://30525, maa://20859, *maa://28188, maa://30524</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>maa://28072</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>maa://45572, maa://27794, maa://20960</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>maa://20972</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2708,12 +2708,12 @@
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>maa://20874</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2730,12 +2730,12 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>maa://20885</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2752,12 @@
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>maa://20886</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>maa://24472, *maa://35841</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2796,12 +2796,12 @@
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>maa://44402</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>*maa://28190, maa://20880</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2840,12 +2840,12 @@
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>maa://24609</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>maa://20890</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2884,12 @@
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>maa://20984</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>maa://40157</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2928,12 +2928,12 @@
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>maa://20927</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>*maa://20926</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>maa://20991, maa://51015</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>maa://20967</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3016,12 @@
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>maa://20929</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>maa://20852</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>maa://45572, maa://27794, *maa://20893</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3082,12 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>maa://40517, *maa://39240</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>*maa://29094, maa://28904</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>*maa://20966</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>maa://39143</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>maa://45572, maa://27794, maa://20843, **maa://24483</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>maa://20894</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3214,12 +3214,12 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>maa://25018, maa://51881, maa://25776, maa://28361, maa://25772, maa://32653, maa://25161, maa://45194, maa://56588</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>maa://45259</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>maa://20887</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>*maa://28554</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>maa://20933, maa://20822</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>maa://29037</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>maa://20904</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>maa://20908, maa://35723, *maa://23346, maa://38822</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3390,12 +3390,12 @@
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>maa://29659, maa://29031</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3412,12 +3412,12 @@
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>maa://31560, maa://20940</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>maa://20986</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>maa://31560, maa://20851</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>maa://20949</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3500,12 @@
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>maa://20869, maa://44690</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>maa://29650, maa://45570</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>maa://20868</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>*maa://20909</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>maa://44403</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>maa://30501</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3632,12 +3632,12 @@
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>maa://20914, maa://31937, maa://20829</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>maa://37484, maa://24611</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>maa://24491, maa://24493</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>maa://21422</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3720,12 +3720,12 @@
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>maa://30719</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>maa://20837, maa://37666</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>maa://29023, maa://39515</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3786,12 +3786,12 @@
       </c>
       <c r="C134" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>maa://39146</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>maa://20856</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>maa://20913</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3852,12 +3852,12 @@
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>maa://41856</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3874,12 @@
       </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>maa://29025</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>**maa://30679, maa://45258</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>maa://20981</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>maa://37689</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3962,12 +3962,12 @@
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>maa://28484, maa://31185, maa://30306</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3984,12 +3984,12 @@
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>maa://30670, maa://31470, *maa://45066</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4006,12 +4006,12 @@
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>maa://20971</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4028,12 +4028,12 @@
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>maa://39147</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>maa://20898</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4072,12 +4072,12 @@
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>maa://29056</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>maa://28828, maa://20846, **maa://47286</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>maa://36641, maa://40957, maa://36865, maa://44635, maa://44660, maa://41128, maa://42918, maa://44119, maa://46108, maa://37300, maa://42917</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>maa://51549, maa://51923</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4160,12 +4160,12 @@
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>maa://20961</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4182,12 +4182,12 @@
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>maa://20963</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>maa://39148</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>maa://20946, maa://20833</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>maa://20945</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="C156" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>maa://37694</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>**maa://39149</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="C158" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>maa://20959</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>maa://44232, maa://45603, maa://44305</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C160" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>maa://20936</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>maa://20855</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4402,12 @@
       </c>
       <c r="C162" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>maa://40158</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>*maa://32845, maa://29054</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4446,12 +4446,12 @@
       </c>
       <c r="C164" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>maa://20973</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>maa://39150</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="C166" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>maa://20975, maa://30806, *maa://47950</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>maa://29633, maa://29627, maa://29659, maa://49074, **maa://30679, maa://29861, maa://42343</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="C168" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>maa://49655, maa://49867</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>maa://29059</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4578,12 +4578,12 @@
       </c>
       <c r="C170" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>maa://45556</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>maa://40159</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4622,12 +4622,12 @@
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>maa://39152</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4644,12 +4644,12 @@
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>*maa://20905</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4666,78 +4666,78 @@
       </c>
       <c r="C174" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>maa://32418, maa://51440</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="15" t="inlineStr">
         <is>
-          <t>豆苗</t>
+          <t>山</t>
         </is>
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>S3-7</t>
+          <t>LE-5</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>maa://37690</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="15" t="inlineStr">
         <is>
-          <t>爱丽丝</t>
+          <t>豆苗</t>
         </is>
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>S3-7</t>
         </is>
       </c>
       <c r="C176" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>maa://20842</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="15" t="inlineStr">
         <is>
-          <t>空弦</t>
+          <t>爱丽丝</t>
         </is>
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>maa://20912</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4749,105 +4749,105 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>maa://20911, *maa://29012</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="15" t="inlineStr">
         <is>
-          <t>图耶</t>
+          <t>空弦</t>
         </is>
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>maa://20964</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="15" t="inlineStr">
         <is>
-          <t>炎狱炎熔</t>
+          <t>图耶</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>WR-4</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C180" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>maa://20983</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="15" t="inlineStr">
         <is>
-          <t>乌有</t>
+          <t>炎狱炎熔</t>
         </is>
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>WR-4</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>maa://31560, *maa://20968</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="15" t="inlineStr">
         <is>
-          <t>嵯峨</t>
+          <t>乌有</t>
         </is>
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>WR-3</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C182" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>maa://28104</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4859,39 +4859,39 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>WR-1</t>
+          <t>WR-3</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>maa://20861</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="15" t="inlineStr">
         <is>
-          <t>夕</t>
+          <t>嵯峨</t>
         </is>
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>WR-1</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>maa://20970</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4903,105 +4903,105 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>maa://20969, maa://41303</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="15" t="inlineStr">
         <is>
-          <t>战车</t>
+          <t>夕</t>
         </is>
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C186" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>maa://20999</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="15" t="inlineStr">
         <is>
-          <t>闪击</t>
+          <t>战车</t>
         </is>
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>maa://35198</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="15" t="inlineStr">
         <is>
-          <t>霜华</t>
+          <t>闪击</t>
         </is>
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>maa://39153</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="15" t="inlineStr">
         <is>
-          <t>灰烬</t>
+          <t>霜华</t>
         </is>
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>SV-8</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>maa://34866, maa://34714</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5013,83 +5013,83 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>SV-8</t>
         </is>
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>maa://34883, maa://20895</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="15" t="inlineStr">
         <is>
-          <t>暴雨</t>
+          <t>灰烬</t>
         </is>
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>maa://20853</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="15" t="inlineStr">
         <is>
-          <t>熔泉</t>
+          <t>暴雨</t>
         </is>
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>maa://20942</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="15" t="inlineStr">
         <is>
-          <t>异客</t>
+          <t>熔泉</t>
         </is>
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>maa://20992</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5101,61 +5101,61 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>*maa://28190, maa://20994</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="15" t="inlineStr">
         <is>
-          <t>赤冬</t>
+          <t>异客</t>
         </is>
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>maa://20860</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="15" t="inlineStr">
         <is>
-          <t>歌蕾蒂娅</t>
+          <t>赤冬</t>
         </is>
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>SV-EX-5</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>maa://44224, maa://35854, maa://25760, maa://50388, **maa://20872, maa://51066</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5167,39 +5167,39 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>SN-EX-3</t>
+          <t>SV-EX-5</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>maa://39156, *maa://39550, *maa://53417</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="15" t="inlineStr">
         <is>
-          <t>凯尔希</t>
+          <t>歌蕾蒂娅</t>
         </is>
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>SN-EX-3</t>
         </is>
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>maa://27823, *maa://28190, maa://22894, *maa://20906</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5216,41 +5216,41 @@
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>maa://27823, *maa://28190, maa://22894, *maa://20906</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="15" t="inlineStr">
         <is>
-          <t>浊心斯卡蒂</t>
+          <t>凯尔希</t>
         </is>
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>maa://42223, maa://49077, maa://42292, maa://42402</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="15" t="inlineStr">
         <is>
-          <t>深靛</t>
+          <t>浊心斯卡蒂</t>
         </is>
       </c>
       <c r="B201" s="15" t="inlineStr">
@@ -5260,78 +5260,78 @@
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>maa://39154</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="15" t="inlineStr">
         <is>
-          <t>贝娜</t>
+          <t>深靛</t>
         </is>
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C202" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>maa://20854</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="15" t="inlineStr">
         <is>
-          <t>绮良</t>
+          <t>贝娜</t>
         </is>
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>maa://20937</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="15" t="inlineStr">
         <is>
-          <t>卡涅利安</t>
+          <t>绮良</t>
         </is>
       </c>
       <c r="B204" s="15" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C204" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>maa://22468</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5343,39 +5343,39 @@
       </c>
       <c r="B205" s="15" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>maa://30673, maa://30672</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="15" t="inlineStr">
         <is>
-          <t>帕拉斯</t>
+          <t>卡涅利安</t>
         </is>
       </c>
       <c r="B206" s="15" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>maa://20934, maa://20827, maa://20828</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5387,83 +5387,83 @@
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>maa://20935</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="15" t="inlineStr">
         <is>
-          <t>龙舌兰</t>
+          <t>帕拉斯</t>
         </is>
       </c>
       <c r="B208" s="15" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C208" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D208" s="10" t="inlineStr">
         <is>
-          <t>maa://53354</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="15" t="inlineStr">
         <is>
-          <t>羽毛笔</t>
+          <t>龙舌兰</t>
         </is>
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>maa://28133, maa://25369</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="15" t="inlineStr">
         <is>
-          <t>水月</t>
+          <t>羽毛笔</t>
         </is>
       </c>
       <c r="B210" s="15" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>maa://20956, *maa://20830, maa://44703</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5475,105 +5475,105 @@
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>*maa://20955</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="15" t="inlineStr">
         <is>
-          <t>假日威龙陈</t>
+          <t>水月</t>
         </is>
       </c>
       <c r="B212" s="15" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C212" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
         <is>
-          <t>maa://39238</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="15" t="inlineStr">
         <is>
-          <t>罗比菈塔</t>
+          <t>假日威龙陈</t>
         </is>
       </c>
       <c r="B213" s="15" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>maa://45261</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="15" t="inlineStr">
         <is>
-          <t>桑葚</t>
+          <t>罗比菈塔</t>
         </is>
       </c>
       <c r="B214" s="15" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C214" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D214" s="10" t="inlineStr">
         <is>
-          <t>maa://39694</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="15" t="inlineStr">
         <is>
-          <t>琴柳</t>
+          <t>桑葚</t>
         </is>
       </c>
       <c r="B215" s="15" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>maa://24636, maa://25778</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5585,51 +5585,51 @@
       </c>
       <c r="B216" s="15" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C216" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D216" s="10" t="inlineStr">
         <is>
-          <t>maa://48261</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="15" t="inlineStr">
         <is>
-          <t>灰毫</t>
+          <t>琴柳</t>
         </is>
       </c>
       <c r="B217" s="15" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D217" s="10" t="inlineStr">
         <is>
-          <t>*maa://39157</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="15" t="inlineStr">
         <is>
-          <t>远牙</t>
+          <t>灰毫</t>
         </is>
       </c>
       <c r="B218" s="15" t="inlineStr">
         <is>
-          <t>S2-2</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="C218" s="12" t="inlineStr">
@@ -5651,127 +5651,127 @@
       </c>
       <c r="B219" s="15" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>S2-2</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D219" s="10" t="inlineStr">
         <is>
-          <t>maa://26499</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="15" t="inlineStr">
         <is>
-          <t>布丁</t>
+          <t>远牙</t>
         </is>
       </c>
       <c r="B220" s="15" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C220" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>maa://20858</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="15" t="inlineStr">
         <is>
-          <t>蜜莓</t>
+          <t>布丁</t>
         </is>
       </c>
       <c r="B221" s="15" t="inlineStr">
         <is>
-          <t>GA-2</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
         <is>
-          <t>maa://39695</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="15" t="inlineStr">
         <is>
-          <t>野鬃</t>
+          <t>蜜莓</t>
         </is>
       </c>
       <c r="B222" s="15" t="inlineStr">
         <is>
-          <t>MN-2</t>
+          <t>GA-2</t>
         </is>
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>maa://20988</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="15" t="inlineStr">
         <is>
-          <t>蚀清</t>
+          <t>野鬃</t>
         </is>
       </c>
       <c r="B223" s="15" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>MN-2</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
-          <t>maa://39158</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="15" t="inlineStr">
         <is>
-          <t>焰尾</t>
+          <t>蚀清</t>
         </is>
       </c>
       <c r="B224" s="15" t="inlineStr">
         <is>
-          <t>NL-5</t>
+          <t>BI-6</t>
         </is>
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D224" s="10" t="inlineStr">
         <is>
-          <t>maa://28187, maa://43531, maa://39520</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5783,39 +5783,39 @@
       </c>
       <c r="B225" s="15" t="inlineStr">
         <is>
-          <t>NL-3</t>
+          <t>NL-5</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D225" s="10" t="inlineStr">
         <is>
-          <t>maa://20985</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="15" t="inlineStr">
         <is>
-          <t>耀骑士临光</t>
+          <t>焰尾</t>
         </is>
       </c>
       <c r="B226" s="15" t="inlineStr">
         <is>
-          <t>MN-8</t>
+          <t>NL-3</t>
         </is>
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D226" s="10" t="inlineStr">
         <is>
-          <t>maa://20987, *maa://35801</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5827,83 +5827,83 @@
       </c>
       <c r="B227" s="15" t="inlineStr">
         <is>
-          <t>NL-10</t>
+          <t>MN-8</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D227" s="10" t="inlineStr">
         <is>
-          <t>*maa://29644, maa://39159</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="15" t="inlineStr">
         <is>
-          <t>耶拉</t>
+          <t>耀骑士临光</t>
         </is>
       </c>
       <c r="B228" s="15" t="inlineStr">
         <is>
-          <t>BI-7</t>
+          <t>NL-10</t>
         </is>
       </c>
       <c r="C228" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D228" s="10" t="inlineStr">
         <is>
-          <t>maa://30677</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="15" t="inlineStr">
         <is>
-          <t>极光</t>
+          <t>耶拉</t>
         </is>
       </c>
       <c r="B229" s="15" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>BI-7</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D229" s="10" t="inlineStr">
         <is>
-          <t>maa://20896</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="15" t="inlineStr">
         <is>
-          <t>灵知</t>
+          <t>极光</t>
         </is>
       </c>
       <c r="B230" s="15" t="inlineStr">
         <is>
-          <t>BI-7</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D230" s="10" t="inlineStr">
         <is>
-          <t>maa://29058, maa://39140, maa://38723</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5915,90 +5915,90 @@
       </c>
       <c r="B231" s="15" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>BI-7</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>*maa://48263</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="15" t="inlineStr">
         <is>
-          <t>九色鹿</t>
+          <t>灵知</t>
         </is>
       </c>
       <c r="B232" s="15" t="inlineStr">
         <is>
-          <t>IW-3</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D232" s="10" t="inlineStr">
         <is>
-          <t>maa://39160</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="15" t="inlineStr">
         <is>
-          <t>寒芒克洛丝</t>
+          <t>九色鹿</t>
         </is>
       </c>
       <c r="B233" s="15" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>IW-3</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D233" s="10" t="inlineStr">
         <is>
-          <t>maa://49491</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="15" t="inlineStr">
         <is>
-          <t>夜半</t>
+          <t>寒芒克洛丝</t>
         </is>
       </c>
       <c r="B234" s="15" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C234" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D234" s="10" t="inlineStr">
         <is>
-          <t>maa://35952</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="15" t="inlineStr">
         <is>
-          <t>老鲤</t>
+          <t>夜半</t>
         </is>
       </c>
       <c r="B235" s="15" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D235" s="10" t="inlineStr">
         <is>
-          <t>maa://20917</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6025,149 +6025,149 @@
       </c>
       <c r="B236" s="15" t="inlineStr">
         <is>
-          <t>IW-EX-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C236" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D236" s="10" t="inlineStr">
         <is>
-          <t>maa://30714, maa://30675</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="15" t="inlineStr">
         <is>
-          <t>令</t>
+          <t>老鲤</t>
         </is>
       </c>
       <c r="B237" s="15" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>IW-EX-1</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D237" s="13" t="inlineStr">
         <is>
-          <t>maa://20922, *maa://32623, maa://34242</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="15" t="inlineStr">
         <is>
-          <t>夏栎</t>
+          <t>令</t>
         </is>
       </c>
       <c r="B238" s="15" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C238" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D238" s="10" t="inlineStr">
         <is>
-          <t>maa://32999</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="15" t="inlineStr">
         <is>
-          <t>澄闪</t>
+          <t>夏栎</t>
         </is>
       </c>
       <c r="B239" s="15" t="inlineStr">
         <is>
-          <t>R8-8</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D239" s="10" t="inlineStr">
         <is>
-          <t>*maa://30667, maa://30666, *maa://30723, maa://39588</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="15" t="inlineStr">
         <is>
-          <t>见行者</t>
+          <t>澄闪</t>
         </is>
       </c>
       <c r="B240" s="15" t="inlineStr">
         <is>
-          <t>GA-EX-1</t>
+          <t>R8-8</t>
         </is>
       </c>
       <c r="C240" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D240" s="10" t="inlineStr">
         <is>
-          <t>maa://30512</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="15" t="inlineStr">
         <is>
-          <t>风丸</t>
+          <t>见行者</t>
         </is>
       </c>
       <c r="B241" s="15" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>GA-EX-1</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D241" s="10" t="inlineStr">
         <is>
-          <t>maa://20870</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="15" t="inlineStr">
         <is>
-          <t>菲亚梅塔</t>
+          <t>风丸</t>
         </is>
       </c>
       <c r="B242" s="15" t="inlineStr">
         <is>
-          <t>GA-4</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C242" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D242" s="10" t="inlineStr">
         <is>
-          <t>maa://29024</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6179,105 +6179,105 @@
       </c>
       <c r="B243" s="15" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>GA-4</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D243" s="10" t="inlineStr">
         <is>
-          <t>maa://20867, maa://38485, *maa://32202</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="15" t="inlineStr">
         <is>
-          <t>褐果</t>
+          <t>菲亚梅塔</t>
         </is>
       </c>
       <c r="B244" s="15" t="inlineStr">
         <is>
-          <t>SV-3</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C244" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>maa://40160</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="15" t="inlineStr">
         <is>
-          <t>海蒂</t>
+          <t>褐果</t>
         </is>
       </c>
       <c r="B245" s="15" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>SV-3</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D245" s="10" t="inlineStr">
         <is>
-          <t>maa://43089</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="15" t="inlineStr">
         <is>
-          <t>洛洛</t>
+          <t>海蒂</t>
         </is>
       </c>
       <c r="B246" s="15" t="inlineStr">
         <is>
-          <t>RI-EX-4</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C246" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D246" s="10" t="inlineStr">
         <is>
-          <t>maa://30674</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="15" t="inlineStr">
         <is>
-          <t>号角</t>
+          <t>洛洛</t>
         </is>
       </c>
       <c r="B247" s="15" t="inlineStr">
         <is>
-          <t>7-15</t>
+          <t>RI-EX-4</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D247" s="10" t="inlineStr">
         <is>
-          <t>maa://28923, maa://28906</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6289,61 +6289,61 @@
       </c>
       <c r="B248" s="15" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>7-15</t>
         </is>
       </c>
       <c r="C248" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D248" s="10" t="inlineStr">
         <is>
-          <t>maa://42287, maa://45570, maa://42225</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="15" t="inlineStr">
         <is>
-          <t>掠风</t>
+          <t>号角</t>
         </is>
       </c>
       <c r="B249" s="15" t="inlineStr">
         <is>
-          <t>11-9</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D249" s="13" t="inlineStr">
         <is>
-          <t>maa://39161</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="15" t="inlineStr">
         <is>
-          <t>流明</t>
+          <t>掠风</t>
         </is>
       </c>
       <c r="B250" s="15" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>11-9</t>
         </is>
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D250" s="10" t="inlineStr">
         <is>
-          <t>maa://20923</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6355,39 +6355,39 @@
       </c>
       <c r="B251" s="15" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D251" s="10" t="inlineStr">
         <is>
-          <t>maa://24093, maa://31559, maa://20924, *maa://49440</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="15" t="inlineStr">
         <is>
-          <t>艾丽妮</t>
+          <t>流明</t>
         </is>
       </c>
       <c r="B252" s="15" t="inlineStr">
         <is>
-          <t>SV-EX-1</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C252" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D252" s="10" t="inlineStr">
         <is>
-          <t>maa://40958, *maa://45067</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6399,39 +6399,39 @@
       </c>
       <c r="B253" s="15" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>SV-EX-1</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D253" s="10" t="inlineStr">
         <is>
-          <t>maa://20840</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="15" t="inlineStr">
         <is>
-          <t>归溟幽灵鲨</t>
+          <t>艾丽妮</t>
         </is>
       </c>
       <c r="B254" s="15" t="inlineStr">
         <is>
-          <t>SV-EX-1</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C254" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D254" s="10" t="inlineStr">
         <is>
-          <t>maa://20877, *maa://45067, maa://20836, maa://20632</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6443,83 +6443,83 @@
       </c>
       <c r="B255" s="15" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>SV-EX-1</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D255" s="10" t="inlineStr">
         <is>
-          <t>maa://20879, maa://20834</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="15" t="inlineStr">
         <is>
-          <t>埃拉托</t>
+          <t>归溟幽灵鲨</t>
         </is>
       </c>
       <c r="B256" s="15" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>S4-1</t>
         </is>
       </c>
       <c r="C256" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D256" s="10" t="inlineStr">
         <is>
-          <t>maa://20839</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="15" t="inlineStr">
         <is>
-          <t>濯尘芙蓉</t>
+          <t>埃拉托</t>
         </is>
       </c>
       <c r="B257" s="15" t="inlineStr">
         <is>
-          <t>LE-4</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D257" s="10" t="inlineStr">
         <is>
-          <t>maa://30676</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="15" t="inlineStr">
         <is>
-          <t>黑键</t>
+          <t>濯尘芙蓉</t>
         </is>
       </c>
       <c r="B258" s="15" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C258" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D258" s="10" t="inlineStr">
         <is>
-          <t>maa://31560, maa://20884</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6531,17 +6531,17 @@
       </c>
       <c r="B259" s="15" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D259" s="10" t="inlineStr">
         <is>
-          <t>maa://47204</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6553,95 +6553,95 @@
       </c>
       <c r="B260" s="15" t="inlineStr">
         <is>
-          <t>11-12</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C260" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D260" s="10" t="inlineStr">
         <is>
-          <t>maa://29027</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="15" t="inlineStr">
         <is>
-          <t>星源</t>
+          <t>黑键</t>
         </is>
       </c>
       <c r="B261" s="15" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>11-12</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D261" s="10" t="inlineStr">
         <is>
-          <t>maa://20977</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="15" t="inlineStr">
         <is>
-          <t>承曦格雷伊</t>
+          <t>星源</t>
         </is>
       </c>
       <c r="B262" s="15" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D262" s="10" t="inlineStr">
         <is>
-          <t>maa://39162</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="15" t="inlineStr">
         <is>
-          <t>多萝西</t>
+          <t>承曦格雷伊</t>
         </is>
       </c>
       <c r="B263" s="15" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D263" s="10" t="inlineStr">
         <is>
-          <t>maa://22467</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="15" t="inlineStr">
         <is>
-          <t>至简</t>
+          <t>多萝西</t>
         </is>
       </c>
       <c r="B264" s="15" t="inlineStr">
         <is>
-          <t>IC-8</t>
+          <t>MB-EX-1</t>
         </is>
       </c>
       <c r="C264" s="12" t="inlineStr">
@@ -6658,975 +6658,975 @@
     <row r="265">
       <c r="A265" s="15" t="inlineStr">
         <is>
-          <t>晓歌</t>
+          <t>多萝西</t>
         </is>
       </c>
       <c r="B265" s="15" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D265" s="10" t="inlineStr">
         <is>
-          <t>maa://49643</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="15" t="inlineStr">
         <is>
-          <t>鸿雪</t>
+          <t>至简</t>
         </is>
       </c>
       <c r="B266" s="15" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>IC-8</t>
         </is>
       </c>
       <c r="C266" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D266" s="10" t="inlineStr">
         <is>
-          <t>maa://48265</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="15" t="inlineStr">
         <is>
-          <t>鸿雪</t>
+          <t>晓歌</t>
         </is>
       </c>
       <c r="B267" s="15" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D267" s="10" t="inlineStr">
         <is>
-          <t>*maa://20825, *maa://21445, *maa://35726</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="15" t="inlineStr">
         <is>
-          <t>百炼嘉维尔</t>
+          <t>鸿雪</t>
         </is>
       </c>
       <c r="B268" s="15" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C268" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D268" s="10" t="inlineStr">
         <is>
-          <t>maa://25769</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="15" t="inlineStr">
         <is>
-          <t>但书</t>
+          <t>鸿雪</t>
         </is>
       </c>
       <c r="B269" s="15" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D269" s="10" t="inlineStr">
         <is>
-          <t>maa://20862</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="15" t="inlineStr">
         <is>
-          <t>玛恩纳</t>
+          <t>百炼嘉维尔</t>
         </is>
       </c>
       <c r="B270" s="15" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C270" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D270" s="10" t="inlineStr">
         <is>
-          <t>maa://51881, maa://51630, maa://51893, *maa://55171, maa://56588</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="15" t="inlineStr">
         <is>
-          <t>罗小黑</t>
+          <t>但书</t>
         </is>
       </c>
       <c r="B271" s="15" t="inlineStr">
         <is>
-          <t>IW-4</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D271" s="10" t="inlineStr">
         <is>
-          <t>maa://39163</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="15" t="inlineStr">
         <is>
-          <t>海沫</t>
+          <t>玛恩纳</t>
         </is>
       </c>
       <c r="B272" s="15" t="inlineStr">
         <is>
-          <t>SN-2</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C272" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D272" s="10" t="inlineStr">
         <is>
-          <t>maa://29061</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="15" t="inlineStr">
         <is>
-          <t>铅踝</t>
+          <t>罗小黑</t>
         </is>
       </c>
       <c r="B273" s="15" t="inlineStr">
         <is>
-          <t>S3-5</t>
+          <t>IW-4</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D273" s="10" t="inlineStr">
         <is>
-          <t>maa://20939</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="15" t="inlineStr">
         <is>
-          <t>达格达</t>
+          <t>海沫</t>
         </is>
       </c>
       <c r="B274" s="15" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>SN-2</t>
         </is>
       </c>
       <c r="C274" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D274" s="10" t="inlineStr">
         <is>
-          <t>maa://39164</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="15" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>铅踝</t>
         </is>
       </c>
       <c r="B275" s="15" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>S3-5</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D275" s="10" t="inlineStr">
         <is>
-          <t>maa://28133, maa://33394</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="15" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>达格达</t>
         </is>
       </c>
       <c r="B276" s="15" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="C276" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D276" s="10" t="inlineStr">
         <is>
-          <t>maa://42311</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="15" t="inlineStr">
         <is>
-          <t>石英</t>
+          <t>白铁</t>
         </is>
       </c>
       <c r="B277" s="15" t="inlineStr">
         <is>
-          <t>DH-4</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D277" s="10" t="inlineStr">
         <is>
-          <t>maa://41362</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="15" t="inlineStr">
         <is>
-          <t>雪绒</t>
+          <t>白铁</t>
         </is>
       </c>
       <c r="B278" s="15" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C278" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D278" s="10" t="inlineStr">
         <is>
-          <t>maa://20978</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="15" t="inlineStr">
         <is>
-          <t>子月</t>
+          <t>石英</t>
         </is>
       </c>
       <c r="B279" s="15" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>DH-4</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D279" s="10" t="inlineStr">
         <is>
-          <t>maa://21002</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="15" t="inlineStr">
         <is>
-          <t>伺夜</t>
+          <t>雪绒</t>
         </is>
       </c>
       <c r="B280" s="15" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C280" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D280" s="10" t="inlineStr">
         <is>
-          <t>*maa://39165</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="15" t="inlineStr">
         <is>
-          <t>伺夜</t>
+          <t>子月</t>
         </is>
       </c>
       <c r="B281" s="15" t="inlineStr">
         <is>
-          <t>IS-6</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D281" s="10" t="inlineStr">
         <is>
-          <t>maa://48267, maa://48266</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="15" t="inlineStr">
         <is>
-          <t>斥罪</t>
+          <t>伺夜</t>
         </is>
       </c>
       <c r="B282" s="15" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C282" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D282" s="10" t="inlineStr">
         <is>
-          <t>maa://29635</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="15" t="inlineStr">
         <is>
-          <t>斥罪</t>
+          <t>伺夜</t>
         </is>
       </c>
       <c r="B283" s="15" t="inlineStr">
         <is>
-          <t>IS-7</t>
+          <t>IS-6</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D283" s="10" t="inlineStr">
         <is>
-          <t>maa://38296</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="15" t="inlineStr">
         <is>
-          <t>缄默德克萨斯</t>
+          <t>斥罪</t>
         </is>
       </c>
       <c r="B284" s="15" t="inlineStr">
         <is>
-          <t>CB-8</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C284" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D284" s="10" t="inlineStr">
         <is>
-          <t>maa://20899, maa://46332</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="15" t="inlineStr">
         <is>
-          <t>谜图</t>
+          <t>斥罪</t>
         </is>
       </c>
       <c r="B285" s="15" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>IS-7</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D285" s="10" t="inlineStr">
         <is>
-          <t>maa://53353</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="15" t="inlineStr">
         <is>
-          <t>和弦</t>
+          <t>缄默德克萨斯</t>
         </is>
       </c>
       <c r="B286" s="15" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>CB-8</t>
         </is>
       </c>
       <c r="C286" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D286" s="10" t="inlineStr">
         <is>
-          <t>maa://20881</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="15" t="inlineStr">
         <is>
-          <t>焰影苇草</t>
+          <t>谜图</t>
         </is>
       </c>
       <c r="B287" s="15" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D287" s="10" t="inlineStr">
         <is>
-          <t>maa://30710, maa://36845, maa://31558, maa://30668</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="15" t="inlineStr">
         <is>
-          <t>截云</t>
+          <t>和弦</t>
         </is>
       </c>
       <c r="B288" s="15" t="inlineStr">
         <is>
-          <t>S2-2</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C288" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D288" s="10" t="inlineStr">
         <is>
-          <t>maa://20902</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="15" t="inlineStr">
         <is>
-          <t>火哨</t>
+          <t>焰影苇草</t>
         </is>
       </c>
       <c r="B289" s="15" t="inlineStr">
         <is>
-          <t>S4-6</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D289" s="10" t="inlineStr">
         <is>
-          <t>maa://29159</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="15" t="inlineStr">
         <is>
-          <t>林</t>
+          <t>截云</t>
         </is>
       </c>
       <c r="B290" s="15" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>S2-2</t>
         </is>
       </c>
       <c r="C290" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D290" s="10" t="inlineStr">
         <is>
-          <t>maa://25774, maa://28133, maa://22469, **maa://31349</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="15" t="inlineStr">
         <is>
-          <t>林</t>
+          <t>火哨</t>
         </is>
       </c>
       <c r="B291" s="15" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>S4-6</t>
         </is>
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D291" s="10" t="inlineStr">
         <is>
-          <t>maa://47882</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="15" t="inlineStr">
         <is>
-          <t>重岳</t>
+          <t>林</t>
         </is>
       </c>
       <c r="B292" s="15" t="inlineStr">
         <is>
-          <t>WB-7</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C292" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D292" s="10" t="inlineStr">
         <is>
-          <t>maa://32414, maa://32505, maa://39155</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="15" t="inlineStr">
         <is>
-          <t>重岳</t>
+          <t>林</t>
         </is>
       </c>
       <c r="B293" s="15" t="inlineStr">
         <is>
-          <t>GA-5</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D293" s="10" t="inlineStr">
         <is>
-          <t>maa://45799, maa://57199</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="15" t="inlineStr">
         <is>
-          <t>铎铃</t>
+          <t>重岳</t>
         </is>
       </c>
       <c r="B294" s="15" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>WB-7</t>
         </is>
       </c>
       <c r="C294" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D294" s="10" t="inlineStr">
         <is>
-          <t>maa://42312</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="15" t="inlineStr">
         <is>
-          <t>仇白</t>
+          <t>重岳</t>
         </is>
       </c>
       <c r="B295" s="15" t="inlineStr">
         <is>
-          <t>WB-7</t>
+          <t>GA-5</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D295" s="10" t="inlineStr">
         <is>
-          <t>maa://36642, maa://36867, maa://39155</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="15" t="inlineStr">
         <is>
-          <t>火龙S黑角</t>
+          <t>铎铃</t>
         </is>
       </c>
       <c r="B296" s="15" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C296" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D296" s="10" t="inlineStr">
         <is>
-          <t>**maa://39166, maa://39167</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="15" t="inlineStr">
         <is>
-          <t>麒麟R夜刀</t>
+          <t>仇白</t>
         </is>
       </c>
       <c r="B297" s="15" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>WB-7</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D297" s="10" t="inlineStr">
         <is>
-          <t>maa://29005, maa://31560</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="15" t="inlineStr">
         <is>
-          <t>休谟斯</t>
+          <t>火龙S黑角</t>
         </is>
       </c>
       <c r="B298" s="15" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C298" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D298" s="10" t="inlineStr">
         <is>
-          <t>maa://39168</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="15" t="inlineStr">
         <is>
-          <t>摩根</t>
+          <t>麒麟R夜刀</t>
         </is>
       </c>
       <c r="B299" s="15" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D299" s="10" t="inlineStr">
         <is>
-          <t>maa://39169</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="15" t="inlineStr">
         <is>
-          <t>洋灰</t>
+          <t>休谟斯</t>
         </is>
       </c>
       <c r="B300" s="15" t="inlineStr">
         <is>
-          <t>IW-EX-6</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C300" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D300" s="10" t="inlineStr">
         <is>
-          <t>maa://39170</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="15" t="inlineStr">
         <is>
-          <t>伊内丝</t>
+          <t>摩根</t>
         </is>
       </c>
       <c r="B301" s="15" t="inlineStr">
         <is>
-          <t>12-12</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D301" s="10" t="inlineStr">
         <is>
-          <t>maa://50280, maa://49642, maa://49660, *maa://50517</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="15" t="inlineStr">
         <is>
-          <t>玫拉</t>
+          <t>洋灰</t>
         </is>
       </c>
       <c r="B302" s="15" t="inlineStr">
         <is>
-          <t>S3-5</t>
+          <t>IW-EX-6</t>
         </is>
       </c>
       <c r="C302" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D302" s="10" t="inlineStr">
         <is>
-          <t>maa://39171</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="15" t="inlineStr">
         <is>
-          <t>淬羽赫默</t>
+          <t>伊内丝</t>
         </is>
       </c>
       <c r="B303" s="15" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>12-12</t>
         </is>
       </c>
       <c r="C303" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D303" s="10" t="inlineStr">
         <is>
-          <t>maa://27939</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="15" t="inlineStr">
         <is>
-          <t>淬羽赫默</t>
+          <t>玫拉</t>
         </is>
       </c>
       <c r="B304" s="15" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>S3-5</t>
         </is>
       </c>
       <c r="C304" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D304" s="10" t="inlineStr">
         <is>
-          <t>maa://53352</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="15" t="inlineStr">
         <is>
-          <t>霍尔海雅</t>
+          <t>淬羽赫默</t>
         </is>
       </c>
       <c r="B305" s="15" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C305" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D305" s="10" t="inlineStr">
         <is>
-          <t>maa://29129</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="15" t="inlineStr">
         <is>
-          <t>霍尔海雅</t>
+          <t>淬羽赫默</t>
         </is>
       </c>
       <c r="B306" s="15" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C306" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D306" s="10" t="inlineStr">
         <is>
-          <t>maa://36005</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="15" t="inlineStr">
         <is>
-          <t>缪尔赛思</t>
+          <t>霍尔海雅</t>
         </is>
       </c>
       <c r="B307" s="15" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C307" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D307" s="10" t="inlineStr">
         <is>
-          <t>maa://35859</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="15" t="inlineStr">
         <is>
-          <t>缪尔赛思</t>
+          <t>霍尔海雅</t>
         </is>
       </c>
       <c r="B308" s="15" t="inlineStr">
         <is>
-          <t>6-12</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C308" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D308" s="10" t="inlineStr">
         <is>
-          <t>maa://53348</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="15" t="inlineStr">
         <is>
-          <t>隐现</t>
+          <t>缪尔赛思</t>
         </is>
       </c>
       <c r="B309" s="15" t="inlineStr">
@@ -7636,398 +7636,398 @@
       </c>
       <c r="C309" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D309" s="10" t="inlineStr">
         <is>
-          <t>**maa://39172</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="15" t="inlineStr">
         <is>
-          <t>空构</t>
+          <t>缪尔赛思</t>
         </is>
       </c>
       <c r="B310" s="15" t="inlineStr">
         <is>
-          <t>DM-2</t>
+          <t>6-12</t>
         </is>
       </c>
       <c r="C310" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D310" s="10" t="inlineStr">
         <is>
-          <t>maa://39173</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="15" t="inlineStr">
         <is>
-          <t>圣约送葬人</t>
+          <t>隐现</t>
         </is>
       </c>
       <c r="B311" s="15" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C311" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D311" s="10" t="inlineStr">
         <is>
-          <t>maa://25775, *maa://25393</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="15" t="inlineStr">
         <is>
-          <t>寒檀</t>
+          <t>空构</t>
         </is>
       </c>
       <c r="B312" s="15" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>DM-2</t>
         </is>
       </c>
       <c r="C312" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D312" s="10" t="inlineStr">
         <is>
-          <t>maa://40161</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="15" t="inlineStr">
         <is>
-          <t>提丰</t>
+          <t>圣约送葬人</t>
         </is>
       </c>
       <c r="B313" s="15" t="inlineStr">
         <is>
-          <t>S2-1</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C313" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D313" s="10" t="inlineStr">
         <is>
-          <t>maa://25367</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="15" t="inlineStr">
         <is>
-          <t>凛视</t>
+          <t>寒檀</t>
         </is>
       </c>
       <c r="B314" s="15" t="inlineStr">
         <is>
-          <t>7-13</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C314" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D314" s="10" t="inlineStr">
         <is>
-          <t>*maa://43090</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="15" t="inlineStr">
         <is>
-          <t>苍苔</t>
+          <t>提丰</t>
         </is>
       </c>
       <c r="B315" s="15" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>S2-1</t>
         </is>
       </c>
       <c r="C315" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D315" s="10" t="inlineStr">
         <is>
-          <t>maa://28070</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="15" t="inlineStr">
         <is>
-          <t>青枳</t>
+          <t>凛视</t>
         </is>
       </c>
       <c r="B316" s="15" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>7-13</t>
         </is>
       </c>
       <c r="C316" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D316" s="10" t="inlineStr">
         <is>
-          <t>maa://28241</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="15" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>苍苔</t>
         </is>
       </c>
       <c r="B317" s="15" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C317" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D317" s="10" t="inlineStr">
         <is>
-          <t>maa://25773, *maa://26088</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="15" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>青枳</t>
         </is>
       </c>
       <c r="B318" s="15" t="inlineStr">
         <is>
-          <t>11-16</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C318" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D318" s="10" t="inlineStr">
         <is>
-          <t>maa://39239</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="15" t="inlineStr">
         <is>
-          <t>纯烬艾雅法拉</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B319" s="15" t="inlineStr">
         <is>
-          <t>FC-5</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C319" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D319" s="10" t="inlineStr">
         <is>
-          <t>maa://39692, maa://39810</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="15" t="inlineStr">
         <is>
-          <t>冰酿</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B320" s="15" t="inlineStr">
         <is>
-          <t>S3-3</t>
+          <t>11-16</t>
         </is>
       </c>
       <c r="C320" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D320" s="10" t="inlineStr">
         <is>
-          <t>*maa://39174</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="15" t="inlineStr">
         <is>
-          <t>杏仁</t>
+          <t>纯烬艾雅法拉</t>
         </is>
       </c>
       <c r="B321" s="15" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>FC-5</t>
         </is>
       </c>
       <c r="C321" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D321" s="10" t="inlineStr">
         <is>
-          <t>maa://39175</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="15" t="inlineStr">
         <is>
-          <t>涤火杰西卡</t>
+          <t>冰酿</t>
         </is>
       </c>
       <c r="B322" s="15" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>S3-3</t>
         </is>
       </c>
       <c r="C322" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D322" s="10" t="inlineStr">
         <is>
-          <t>maa://34867, maa://34715</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="15" t="inlineStr">
         <is>
-          <t>维荻</t>
+          <t>杏仁</t>
         </is>
       </c>
       <c r="B323" s="15" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C323" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D323" s="10" t="inlineStr">
         <is>
-          <t>maa://39176</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="15" t="inlineStr">
         <is>
-          <t>戴菲恩</t>
+          <t>涤火杰西卡</t>
         </is>
       </c>
       <c r="B324" s="15" t="inlineStr">
         <is>
-          <t>WD-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C324" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D324" s="10" t="inlineStr">
         <is>
-          <t>maa://42316</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="15" t="inlineStr">
         <is>
-          <t>刺玫</t>
+          <t>维荻</t>
         </is>
       </c>
       <c r="B325" s="15" t="inlineStr">
         <is>
-          <t>IC-2</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C325" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D325" s="10" t="inlineStr">
         <is>
-          <t>maa://30680</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="15" t="inlineStr">
         <is>
-          <t>赫德雷</t>
+          <t>戴菲恩</t>
         </is>
       </c>
       <c r="B326" s="15" t="inlineStr">
         <is>
-          <t>IW-7</t>
+          <t>WD-6</t>
         </is>
       </c>
       <c r="C326" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D326" s="10" t="inlineStr">
         <is>
-          <t>maa://40956</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="15" t="inlineStr">
         <is>
-          <t>深律</t>
+          <t>刺玫</t>
         </is>
       </c>
       <c r="B327" s="15" t="inlineStr">
         <is>
-          <t>LE-4</t>
+          <t>IC-2</t>
         </is>
       </c>
       <c r="C327" s="12" t="inlineStr">
@@ -8044,1222 +8044,1222 @@
     <row r="328">
       <c r="A328" s="15" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>赫德雷</t>
         </is>
       </c>
       <c r="B328" s="15" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>IW-7</t>
         </is>
       </c>
       <c r="C328" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D328" s="10" t="inlineStr">
         <is>
-          <t>maa://34205, **maa://39541</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="15" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>深律</t>
         </is>
       </c>
       <c r="B329" s="15" t="inlineStr">
         <is>
-          <t>TW-5</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C329" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D329" s="10" t="inlineStr">
         <is>
-          <t>maa://43092, maa://43093</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="15" t="inlineStr">
         <is>
-          <t>薇薇安娜</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B330" s="15" t="inlineStr">
         <is>
-          <t>MN-3</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C330" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D330" s="10" t="inlineStr">
         <is>
-          <t>maa://44234</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="12" t="inlineStr">
         <is>
-          <t>塑心</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B331" s="12" t="inlineStr">
         <is>
-          <t>GA-7</t>
+          <t>TW-5</t>
         </is>
       </c>
       <c r="C331" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D331" s="13" t="inlineStr">
         <is>
-          <t>maa://42968, maa://49245</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="12" t="inlineStr">
         <is>
-          <t>哈洛德</t>
+          <t>薇薇安娜</t>
         </is>
       </c>
       <c r="B332" s="12" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>MN-3</t>
         </is>
       </c>
       <c r="C332" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D332" s="13" t="inlineStr">
         <is>
-          <t>*maa://40162</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="12" t="inlineStr">
         <is>
-          <t>烈夏</t>
+          <t>塑心</t>
         </is>
       </c>
       <c r="B333" s="12" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>GA-7</t>
         </is>
       </c>
       <c r="C333" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D333" s="13" t="inlineStr">
         <is>
-          <t>maa://37692</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="12" t="inlineStr">
         <is>
-          <t>锏</t>
+          <t>哈洛德</t>
         </is>
       </c>
       <c r="B334" s="12" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C334" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D334" s="13" t="inlineStr">
         <is>
-          <t>maa://30671, maa://30669, maa://37275, *maa://32410, maa://41605</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="12" t="inlineStr">
         <is>
-          <t>莱伊</t>
+          <t>烈夏</t>
         </is>
       </c>
       <c r="B335" s="12" t="inlineStr">
         <is>
-          <t>S9-1</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C335" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D335" s="13" t="inlineStr">
         <is>
-          <t>maa://38295, maa://49332</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="12" t="inlineStr">
         <is>
-          <t>万顷</t>
+          <t>锏</t>
         </is>
       </c>
       <c r="B336" s="12" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>BI-6</t>
         </is>
       </c>
       <c r="C336" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D336" s="13" t="inlineStr">
         <is>
-          <t>maa://32417</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="12" t="inlineStr">
         <is>
-          <t>小满</t>
+          <t>莱伊</t>
         </is>
       </c>
       <c r="B337" s="12" t="inlineStr">
         <is>
-          <t>9-11</t>
+          <t>S9-1</t>
         </is>
       </c>
       <c r="C337" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D337" s="13" t="inlineStr">
         <is>
-          <t>maa://32419</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="12" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>万顷</t>
         </is>
       </c>
       <c r="B338" s="12" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C338" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>maa://32416</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="12" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>小满</t>
         </is>
       </c>
       <c r="B339" s="12" t="inlineStr">
         <is>
-          <t>RI-7</t>
+          <t>9-11</t>
         </is>
       </c>
       <c r="C339" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>maa://45800</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="12" t="inlineStr">
         <is>
-          <t>黍</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B340" s="12" t="inlineStr">
         <is>
-          <t>11-11</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C340" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>maa://32647, maa://32415, maa://34677, maa://32892, maa://32653</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="12" t="inlineStr">
         <is>
-          <t>红隼</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B341" s="12" t="inlineStr">
         <is>
-          <t>11-18</t>
+          <t>RI-7</t>
         </is>
       </c>
       <c r="C341" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>maa://32420</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="12" t="inlineStr">
         <is>
-          <t>导火索</t>
+          <t>黍</t>
         </is>
       </c>
       <c r="B342" s="12" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>11-11</t>
         </is>
       </c>
       <c r="C342" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>maa://35606</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="12" t="inlineStr">
         <is>
-          <t>双月</t>
+          <t>红隼</t>
         </is>
       </c>
       <c r="B343" s="12" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>11-18</t>
         </is>
       </c>
       <c r="C343" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>maa://34716</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="12" t="inlineStr">
         <is>
-          <t>医生</t>
+          <t>导火索</t>
         </is>
       </c>
       <c r="B344" s="12" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C344" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>maa://39179</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="12" t="inlineStr">
         <is>
-          <t>艾拉</t>
+          <t>双月</t>
         </is>
       </c>
       <c r="B345" s="12" t="inlineStr">
         <is>
-          <t>DM-EX-1</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C345" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>maa://34865, maa://34717, *maa://45066</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="12" t="inlineStr">
         <is>
-          <t>露托</t>
+          <t>医生</t>
         </is>
       </c>
       <c r="B346" s="12" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C346" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>maa://39180</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="12" t="inlineStr">
         <is>
-          <t>奥达</t>
+          <t>艾拉</t>
         </is>
       </c>
       <c r="B347" s="12" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>DM-EX-1</t>
         </is>
       </c>
       <c r="C347" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>maa://45834, maa://45833</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="12" t="inlineStr">
         <is>
-          <t>阿罗玛</t>
+          <t>露托</t>
         </is>
       </c>
       <c r="B348" s="12" t="inlineStr">
         <is>
-          <t>GT-HX-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C348" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>maa://39181</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="12" t="inlineStr">
         <is>
-          <t>阿斯卡纶</t>
+          <t>奥达</t>
         </is>
       </c>
       <c r="B349" s="12" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C349" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>maa://36868, maa://35996, maa://47349</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="12" t="inlineStr">
         <is>
-          <t>历阵锐枪芬</t>
+          <t>阿罗玛</t>
         </is>
       </c>
       <c r="B350" s="12" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>GT-HX-3</t>
         </is>
       </c>
       <c r="C350" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>maa://36647</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="12" t="inlineStr">
         <is>
-          <t>魔王</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B351" s="12" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C351" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>maa://42299, maa://42224</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="12" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B352" s="12" t="inlineStr">
         <is>
-          <t>14-9</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C352" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>maa://49648, *maa://49662</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="12" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>历阵锐枪芬</t>
         </is>
       </c>
       <c r="B353" s="12" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C353" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>maa://36646, maa://36845, maa://51007</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="12" t="inlineStr">
         <is>
-          <t>维什戴尔</t>
+          <t>魔王</t>
         </is>
       </c>
       <c r="B354" s="12" t="inlineStr">
         <is>
-          <t>DM-5</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C354" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>maa://36645, maa://36841, maa://37484, maa://37858, maa://40489, maa://56268</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="12" t="inlineStr">
         <is>
-          <t>阿米娅</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B355" s="12" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>14-9</t>
         </is>
       </c>
       <c r="C355" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>maa://42635, maa://50629, maa://48859</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="12" t="inlineStr">
         <is>
-          <t>深巡</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B356" s="12" t="inlineStr">
         <is>
-          <t>SN-5</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C356" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>maa://39183</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="12" t="inlineStr">
         <is>
-          <t>海霓</t>
+          <t>维什戴尔</t>
         </is>
       </c>
       <c r="B357" s="12" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>DM-5</t>
         </is>
       </c>
       <c r="C357" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>maa://39184</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="12" t="inlineStr">
         <is>
-          <t>乌尔比安</t>
+          <t>阿米娅</t>
         </is>
       </c>
       <c r="B358" s="12" t="inlineStr">
         <is>
-          <t>SV-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C358" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>maa://40957, maa://44635, maa://48026, maa://41035, maa://44660, maa://41128</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="12" t="inlineStr">
         <is>
-          <t>渡桥</t>
+          <t>深巡</t>
         </is>
       </c>
       <c r="B359" s="12" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>SN-5</t>
         </is>
       </c>
       <c r="C359" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>maa://40164</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="12" t="inlineStr">
         <is>
-          <t>锡人</t>
+          <t>海霓</t>
         </is>
       </c>
       <c r="B360" s="12" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C360" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>maa://48268</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="12" t="inlineStr">
         <is>
-          <t>衡沙</t>
+          <t>乌尔比安</t>
         </is>
       </c>
       <c r="B361" s="12" t="inlineStr">
         <is>
-          <t>DV-2</t>
+          <t>SV-6</t>
         </is>
       </c>
       <c r="C361" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>maa://40165</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="12" t="inlineStr">
         <is>
-          <t>佩佩</t>
+          <t>渡桥</t>
         </is>
       </c>
       <c r="B362" s="12" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C362" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>maa://45798</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="12" t="inlineStr">
         <is>
-          <t>森西</t>
+          <t>锡人</t>
         </is>
       </c>
       <c r="B363" s="12" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C363" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>maa://42331</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="12" t="inlineStr">
         <is>
-          <t>齐尔查克</t>
+          <t>衡沙</t>
         </is>
       </c>
       <c r="B364" s="12" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>DV-2</t>
         </is>
       </c>
       <c r="C364" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>maa://42333, maa://41977, maa://50518</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="12" t="inlineStr">
         <is>
-          <t>莱欧斯</t>
+          <t>佩佩</t>
         </is>
       </c>
       <c r="B365" s="12" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C365" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>maa://42338, maa://41976</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="12" t="inlineStr">
         <is>
-          <t>玛露西尔</t>
+          <t>森西</t>
         </is>
       </c>
       <c r="B366" s="12" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C366" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>maa://41110, maa://45605</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="12" t="inlineStr">
         <is>
-          <t>凯瑟琳</t>
+          <t>齐尔查克</t>
         </is>
       </c>
       <c r="B367" s="12" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C367" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>maa://42343</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="12" t="inlineStr">
         <is>
-          <t>波卜</t>
+          <t>莱欧斯</t>
         </is>
       </c>
       <c r="B368" s="12" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C368" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>maa://43095</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="12" t="inlineStr">
         <is>
-          <t>维娜·维多利亚</t>
+          <t>玛露西尔</t>
         </is>
       </c>
       <c r="B369" s="12" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C369" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>maa://44233, maa://45570</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="12" t="inlineStr">
         <is>
-          <t>裁度</t>
+          <t>凯瑟琳</t>
         </is>
       </c>
       <c r="B370" s="12" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C370" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>maa://43097</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="12" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>波卜</t>
         </is>
       </c>
       <c r="B371" s="12" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C371" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>maa://43872</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="12" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>维娜·维多利亚</t>
         </is>
       </c>
       <c r="B372" s="12" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C372" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>maa://53307</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="12" t="inlineStr">
         <is>
-          <t>忍冬</t>
+          <t>裁度</t>
         </is>
       </c>
       <c r="B373" s="12" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="C373" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>maa://43875</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="12" t="inlineStr">
         <is>
-          <t>荒芜拉普兰德</t>
+          <t>弑君者</t>
         </is>
       </c>
       <c r="B374" s="12" t="inlineStr">
         <is>
-          <t>IS-8</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C374" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>maa://42970, maa://44745, **maa://49516, *maa://45952, maa://44896</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="12" t="inlineStr">
         <is>
-          <t>瑰盐</t>
+          <t>弑君者</t>
         </is>
       </c>
       <c r="B375" s="12" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C375" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>maa://44389</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="12" t="inlineStr">
         <is>
-          <t>引星棘刺</t>
+          <t>忍冬</t>
         </is>
       </c>
       <c r="B376" s="12" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C376" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>maa://48113</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="12" t="inlineStr">
         <is>
-          <t>行箸</t>
+          <t>荒芜拉普兰德</t>
         </is>
       </c>
       <c r="B377" s="12" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>IS-8</t>
         </is>
       </c>
       <c r="C377" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>maa://45807</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="12" t="inlineStr">
         <is>
-          <t>寻澜</t>
+          <t>瑰盐</t>
         </is>
       </c>
       <c r="B378" s="12" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C378" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>maa://50552</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="12" t="inlineStr">
         <is>
-          <t>诺威尔</t>
+          <t>特克诺</t>
         </is>
       </c>
       <c r="B379" s="12" t="inlineStr">
         <is>
-          <t>5-7</t>
+          <t>DH-6</t>
         </is>
       </c>
       <c r="C379" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>maa://47175, maa://47174</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="12" t="inlineStr">
         <is>
-          <t>隐德来希</t>
+          <t>引星棘刺</t>
         </is>
       </c>
       <c r="B380" s="12" t="inlineStr">
         <is>
-          <t>10-12</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C380" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>maa://47023</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="12" t="inlineStr">
         <is>
-          <t>钼铅</t>
+          <t>行箸</t>
         </is>
       </c>
       <c r="B381" s="12" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C381" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>maa://48618</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="12" t="inlineStr">
         <is>
-          <t>骋风</t>
+          <t>寻澜</t>
         </is>
       </c>
       <c r="B382" s="12" t="inlineStr">
         <is>
-          <t>SN-2</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C382" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>maa://51907, maa://51908</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="12" t="inlineStr">
         <is>
-          <t>阿兰娜</t>
+          <t>诺威尔</t>
         </is>
       </c>
       <c r="B383" s="12" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>5-7</t>
         </is>
       </c>
       <c r="C383" s="12" t="inlineStr">
@@ -9276,66 +9276,198 @@
     <row r="384">
       <c r="A384" s="12" t="inlineStr">
         <is>
-          <t>信仰搅拌机</t>
+          <t>隐德来希</t>
         </is>
       </c>
       <c r="B384" s="12" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="C384" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>maa://51898, maa://57241</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="12" t="inlineStr">
         <is>
-          <t>蕾缪安</t>
+          <t>钼铅</t>
         </is>
       </c>
       <c r="B385" s="12" t="inlineStr">
         <is>
-          <t>13-13</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C385" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>maa://51880, maa://51878, maa://56651</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="12" t="inlineStr">
         <is>
+          <t>死芒</t>
+        </is>
+      </c>
+      <c r="B386" s="12" t="inlineStr">
+        <is>
+          <t>4-8</t>
+        </is>
+      </c>
+      <c r="C386" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="12" t="inlineStr">
+        <is>
+          <t>骋风</t>
+        </is>
+      </c>
+      <c r="B387" s="12" t="inlineStr">
+        <is>
+          <t>SN-2</t>
+        </is>
+      </c>
+      <c r="C387" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="12" t="inlineStr">
+        <is>
+          <t>阿兰娜</t>
+        </is>
+      </c>
+      <c r="B388" s="12" t="inlineStr">
+        <is>
+          <t>7-14</t>
+        </is>
+      </c>
+      <c r="C388" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="12" t="inlineStr">
+        <is>
+          <t>信仰搅拌机</t>
+        </is>
+      </c>
+      <c r="B389" s="12" t="inlineStr">
+        <is>
+          <t>14-5</t>
+        </is>
+      </c>
+      <c r="C389" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="12" t="inlineStr">
+        <is>
+          <t>蕾缪安</t>
+        </is>
+      </c>
+      <c r="B390" s="12" t="inlineStr">
+        <is>
+          <t>13-13</t>
+        </is>
+      </c>
+      <c r="C390" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="12" t="inlineStr">
+        <is>
           <t>新约能天使</t>
         </is>
       </c>
-      <c r="B386" s="12" t="inlineStr">
+      <c r="B391" s="12" t="inlineStr">
         <is>
           <t>GA-EX-5</t>
         </is>
       </c>
-      <c r="C386" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>maa://51872, maa://51876, maa://51873</t>
+      <c r="C391" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="12" t="inlineStr">
+        <is>
+          <t>酒神</t>
+        </is>
+      </c>
+      <c r="B392" s="12" t="inlineStr">
+        <is>
+          <t>9-6</t>
+        </is>
+      </c>
+      <c r="C392" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
